--- a/mode_docx_gen/pmi_ka/ksv2_modes/КСВ_2.xlsx
+++ b/mode_docx_gen/pmi_ka/ksv2_modes/КСВ_2.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
